--- a/tests/fixtures/import/tc06-nasa-complete-19-factors.xlsx
+++ b/tests/fixtures/import/tc06-nasa-complete-19-factors.xlsx
@@ -792,6 +792,11 @@
           <t>https://example.org/validation/tech-review</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://example.org/org/reviewer-1</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -819,6 +824,11 @@
           <t>https://example.org/validation/process-check</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://example.org/org/qa-team</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -846,6 +856,11 @@
           <t>https://example.org/validation/deploy-record</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://example.org/system/flight-test-1</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -871,6 +886,11 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>https://example.org/validation/data-source</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://example.org/data/arc-jet-facility</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">

--- a/tests/fixtures/import/tc06-nasa-complete-19-factors.xlsx
+++ b/tests/fixtures/import/tc06-nasa-complete-19-factors.xlsx
@@ -915,7 +915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,6 +964,11 @@
           <t>Factor Status</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linked Evidence</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -999,6 +1004,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>(status)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(URI)</t>
         </is>
       </c>
     </row>
